--- a/协作/15-交付报告.xlsx
+++ b/协作/15-交付报告.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>文档与模板按 v3.4 交付；归档层齐全，快照可还原</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -575,7 +575,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完成,部分完成,阻塞"</formula1>
     </dataValidation>
   </dataValidations>
@@ -735,7 +735,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"新增,修改,删除"</formula1>
     </dataValidation>
   </dataValidations>
